--- a/output/yearly_surface_area_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_12_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497655440965</v>
+        <v>10.84497612980262</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907271614147</v>
+        <v>37.78907123660797</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.46971737098648</v>
+        <v>6.844744994008762</v>
       </c>
       <c r="C2" t="n">
-        <v>12.17563502806894</v>
+        <v>8.021860491400687</v>
       </c>
       <c r="D2" t="n">
-        <v>21.38148325079128</v>
+        <v>27.1472875178328</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.50027472300515</v>
+        <v>16.66025854106837</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9173786285898</v>
+        <v>24.88730430265664</v>
       </c>
       <c r="D3" t="n">
-        <v>81.85812358009906</v>
+        <v>73.7636137585841</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.32943492693298</v>
+        <v>34.59973434077034</v>
       </c>
       <c r="C4" t="n">
-        <v>57.67473238138736</v>
+        <v>50.98706702005809</v>
       </c>
       <c r="D4" t="n">
-        <v>117.4297881480737</v>
+        <v>88.07553179109411</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.14338588921161</v>
+        <v>46.78027810736052</v>
       </c>
       <c r="C5" t="n">
-        <v>89.92808970900784</v>
+        <v>84.6021084134689</v>
       </c>
       <c r="D5" t="n">
-        <v>84.40575887261953</v>
+        <v>65.40894079544375</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.46299367243955</v>
+        <v>45.24286120251001</v>
       </c>
       <c r="C6" t="n">
-        <v>94.10837143369076</v>
+        <v>87.46684821446109</v>
       </c>
       <c r="D6" t="n">
-        <v>51.72337779824321</v>
+        <v>45.80638438474769</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.71616140694821</v>
+        <v>32.09922293805371</v>
       </c>
       <c r="C7" t="n">
-        <v>85.03898614185871</v>
+        <v>73.12155076000668</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>61.58503348740241</v>
+        <v>44.6449768506237</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.679477132172078</v>
+        <v>7.725775451094117</v>
       </c>
       <c r="C21" t="n">
-        <v>93.11366022758644</v>
+        <v>96.57219313867647</v>
       </c>
       <c r="D21" t="n">
-        <v>7.679477132172078</v>
+        <v>8.691497382480883</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.534332793017523</v>
+        <v>7.35329030480861</v>
       </c>
       <c r="C2" t="n">
-        <v>10.72853891200914</v>
+        <v>12.80297181108265</v>
       </c>
       <c r="D2" t="n">
-        <v>29.58398531977338</v>
+        <v>22.78341897245573</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.49045724596268</v>
+        <v>19.99329199698629</v>
       </c>
       <c r="C3" t="n">
-        <v>38.2292556033708</v>
+        <v>28.4706834231575</v>
       </c>
       <c r="D3" t="n">
-        <v>79.76209223153211</v>
+        <v>77.6120647592316</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.14250195249858</v>
+        <v>33.3362250454047</v>
       </c>
       <c r="C4" t="n">
-        <v>64.87290654892499</v>
+        <v>56.28359588446964</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4267450939697</v>
+        <v>103.3142196564131</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.90486225480863</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C5" t="n">
-        <v>96.84941102394787</v>
+        <v>89.41267216427826</v>
       </c>
       <c r="D5" t="n">
-        <v>102.7398972494287</v>
+        <v>79.74245727744719</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.73345731719294</v>
+        <v>54.13847715069036</v>
       </c>
       <c r="C6" t="n">
-        <v>117.2530735613093</v>
+        <v>109.8065172245973</v>
       </c>
       <c r="D6" t="n">
-        <v>64.32214608684252</v>
+        <v>55.18502020341747</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.21439051908685</v>
+        <v>43.23813239043802</v>
       </c>
       <c r="C7" t="n">
-        <v>108.3947640258903</v>
+        <v>99.89086541170445</v>
       </c>
       <c r="D7" t="n">
-        <v>44.79518424937346</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.03594911662541</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>86.03546006166923</v>
+        <v>69.9298889735003</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.31406145436774</v>
+        <v>11.98124898262807</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>42.48905889209769</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,10 +1231,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.859670112573672</v>
+        <v>7.917478164567607</v>
       </c>
       <c r="C21" t="n">
-        <v>101.193252699386</v>
+        <v>105.8962704510917</v>
       </c>
       <c r="D21" t="n">
-        <v>8.842128876645381</v>
+        <v>9.896847705709508</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.80118824212341</v>
+        <v>9.008516934168732</v>
       </c>
       <c r="C2" t="n">
-        <v>10.0962933904742</v>
+        <v>12.90900056314131</v>
       </c>
       <c r="D2" t="n">
-        <v>32.09431419953248</v>
+        <v>27.58416524622263</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.32279937271473</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="C3" t="n">
-        <v>39.92277039319654</v>
+        <v>38.79376053331271</v>
       </c>
       <c r="D3" t="n">
-        <v>82.83496254582462</v>
+        <v>77.16536955379929</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.70031457496002</v>
+        <v>35.03366682604742</v>
       </c>
       <c r="C4" t="n">
-        <v>77.81430478630644</v>
+        <v>62.74153228300516</v>
       </c>
       <c r="D4" t="n">
-        <v>135.4635117273834</v>
+        <v>114.3029217100476</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.91744504851459</v>
+        <v>49.5291716792516</v>
       </c>
       <c r="C5" t="n">
-        <v>105.6851403621692</v>
+        <v>96.03946916794425</v>
       </c>
       <c r="D5" t="n">
-        <v>119.6750451476862</v>
+        <v>95.57313900842701</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.66303352439442</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="C6" t="n">
-        <v>133.353735910957</v>
+        <v>123.572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>78.45047729865838</v>
+        <v>64.76491430145784</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>55.87420709179872</v>
+        <v>52.76010337392783</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7866866485298</v>
+        <v>127.1991595530337</v>
       </c>
       <c r="D7" t="n">
-        <v>50.84373185523806</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.549084370777</v>
+        <v>34.71459882216722</v>
       </c>
       <c r="C8" t="n">
-        <v>110.569335190797</v>
+        <v>97.71825774220626</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>40.88979188187965</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.08281096452199</v>
+        <v>17.86093598336221</v>
       </c>
       <c r="C9" t="n">
-        <v>77.87811838708245</v>
+        <v>62.23593221531803</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>49.11192890494669</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>35.18387422479719</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.023808927521829</v>
+        <v>8.094232633200704</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3243966374849</v>
+        <v>114.3310359439599</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02976115940229</v>
+        <v>11.12956987065097</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.730101496790137</v>
+        <v>8.078801858247003</v>
       </c>
       <c r="C2" t="n">
-        <v>6.865361695797945</v>
+        <v>8.46757394912874</v>
       </c>
       <c r="D2" t="n">
-        <v>26.4698816019025</v>
+        <v>22.4388255282651</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.6719417025281</v>
+        <v>25.89850443803086</v>
       </c>
       <c r="C3" t="n">
-        <v>56.73519982842318</v>
+        <v>55.80253950938871</v>
       </c>
       <c r="D3" t="n">
-        <v>91.54797342101507</v>
+        <v>85.29914928348413</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.26491731589317</v>
+        <v>23.78971036930871</v>
       </c>
       <c r="C4" t="n">
-        <v>95.33751955940777</v>
+        <v>84.08080038251383</v>
       </c>
       <c r="D4" t="n">
-        <v>131.4432548784927</v>
+        <v>109.5807152526205</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.11635461738242</v>
+        <v>34.01755795215198</v>
       </c>
       <c r="C5" t="n">
-        <v>79.66882619962867</v>
+        <v>73.82742735936016</v>
       </c>
       <c r="D5" t="n">
-        <v>79.03069019186825</v>
+        <v>65.2862223324129</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.69692736349078</v>
+        <v>32.76484788153306</v>
       </c>
       <c r="C6" t="n">
-        <v>88.110874708447</v>
+        <v>83.76369587404213</v>
       </c>
       <c r="D6" t="n">
-        <v>33.48937768726721</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.53543771390878</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>77.73281972685395</v>
+        <v>68.68994162303657</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>28.7455727803466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>57.32915718949249</v>
+        <v>45.8132566186774</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.000441968356505</v>
+        <v>5.043237956715865</v>
       </c>
       <c r="C2" t="n">
-        <v>3.673699909291564</v>
+        <v>3.749294482518569</v>
       </c>
       <c r="D2" t="n">
-        <v>18.25854380358218</v>
+        <v>15.97303514809561</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.69081589308704</v>
+        <v>27.69019399828129</v>
       </c>
       <c r="C3" t="n">
-        <v>42.32314353008</v>
+        <v>44.73333414400592</v>
       </c>
       <c r="D3" t="n">
-        <v>91.82286277820418</v>
+        <v>84.94081137143404</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.29190752999335</v>
+        <v>35.4420738710141</v>
       </c>
       <c r="C4" t="n">
-        <v>120.135484820978</v>
+        <v>114.0349045867883</v>
       </c>
       <c r="D4" t="n">
-        <v>146.3373492996211</v>
+        <v>124.5258605543697</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.60785036431157</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C5" t="n">
-        <v>124.6083273615264</v>
+        <v>113.7845589222053</v>
       </c>
       <c r="D5" t="n">
-        <v>99.81919782929447</v>
+        <v>84.72482687649975</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.13719230334986</v>
+        <v>39.40637110076273</v>
       </c>
       <c r="C6" t="n">
-        <v>108.1561993337584</v>
+        <v>102.4404641996334</v>
       </c>
       <c r="D6" t="n">
-        <v>43.27053006467818</v>
+        <v>39.44662275663685</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.15804568485051</v>
+        <v>21.73883941513712</v>
       </c>
       <c r="C7" t="n">
-        <v>97.91460728305563</v>
+        <v>89.88980154854221</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>74.68645660057609</v>
+        <v>61.83537915198535</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.003387211469246</v>
+        <v>6.414739499548659</v>
       </c>
       <c r="C2" t="n">
-        <v>4.288273972150068</v>
+        <v>5.542947538177491</v>
       </c>
       <c r="D2" t="n">
-        <v>28.26549815296992</v>
+        <v>15.74919667152733</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.24702487303848</v>
+        <v>22.32003405605123</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5478405811655</v>
+        <v>28.27924262082937</v>
       </c>
       <c r="D3" t="n">
-        <v>85.57894737919446</v>
+        <v>78.36310175298041</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.71079500453725</v>
+        <v>44.49084246105696</v>
       </c>
       <c r="C4" t="n">
-        <v>112.6820562503362</v>
+        <v>112.8096834518882</v>
       </c>
       <c r="D4" t="n">
-        <v>156.9686951889098</v>
+        <v>137.3779197506647</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.9281621578033</v>
+        <v>44.89041377668541</v>
       </c>
       <c r="C5" t="n">
-        <v>173.2539261069559</v>
+        <v>164.1482161500667</v>
       </c>
       <c r="D5" t="n">
-        <v>124.6574147467388</v>
+        <v>107.4031988446011</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.06676851055134</v>
+        <v>44.88059629964295</v>
       </c>
       <c r="C6" t="n">
-        <v>149.5751532282271</v>
+        <v>140.1965174095573</v>
       </c>
       <c r="D6" t="n">
-        <v>60.01521890831177</v>
+        <v>54.17872880656449</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.57831581772616</v>
+        <v>32.45854259780804</v>
       </c>
       <c r="C7" t="n">
-        <v>125.9415407438936</v>
+        <v>118.874920768725</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2422,10 +2422,10 @@
         <v>15.52143120414207</v>
       </c>
       <c r="C8" t="n">
-        <v>100.1382658331747</v>
+        <v>89.12305659152544</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>63.78905708343648</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.581415625092364</v>
+        <v>3.741440500884595</v>
       </c>
       <c r="C2" t="n">
-        <v>2.058724935805561</v>
+        <v>2.533890824661018</v>
       </c>
       <c r="D2" t="n">
-        <v>19.69385894719101</v>
+        <v>10.90034476025234</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.41883072128167</v>
+        <v>23.86137795171873</v>
       </c>
       <c r="C3" t="n">
-        <v>24.65659359215864</v>
+        <v>27.12568906833937</v>
       </c>
       <c r="D3" t="n">
-        <v>89.45685081096936</v>
+        <v>76.52232480751763</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.04561202941441</v>
+        <v>49.41725244096745</v>
       </c>
       <c r="C4" t="n">
-        <v>107.7428835502704</v>
+        <v>107.7045953898048</v>
       </c>
       <c r="D4" t="n">
-        <v>166.0047010587974</v>
+        <v>146.1586712174481</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.64622064023522</v>
+        <v>47.49204519293946</v>
       </c>
       <c r="C5" t="n">
-        <v>209.1122610045707</v>
+        <v>199.8838325846506</v>
       </c>
       <c r="D5" t="n">
-        <v>131.1124059021616</v>
+        <v>116.4843651088841</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.17115256237099</v>
+        <v>38.80259626265094</v>
       </c>
       <c r="C6" t="n">
-        <v>178.7978553928376</v>
+        <v>174.2494182790622</v>
       </c>
       <c r="D6" t="n">
-        <v>58.24414604985053</v>
+        <v>53.29319237733387</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>131.2714490302495</v>
+        <v>122.3483441463502</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>77.4402589109884</v>
+        <v>69.84644041863932</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>28.39999758845172</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.017311605777948</v>
+        <v>5.182646130718912</v>
       </c>
       <c r="C2" t="n">
-        <v>6.804493338134643</v>
+        <v>6.842781498600268</v>
       </c>
       <c r="D2" t="n">
-        <v>18.16625951938298</v>
+        <v>14.42972775701962</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.60059291528757</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C3" t="n">
-        <v>16.1890196430299</v>
+        <v>17.92671307954676</v>
       </c>
       <c r="D3" t="n">
-        <v>85.52495125546089</v>
+        <v>68.38363633931158</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.29711936815084</v>
+        <v>47.65599705954867</v>
       </c>
       <c r="C4" t="n">
-        <v>86.00797112595031</v>
+        <v>88.29249803373266</v>
       </c>
       <c r="D4" t="n">
-        <v>171.1736027216569</v>
+        <v>150.3320807082013</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.11441648416971</v>
+        <v>59.3466487217197</v>
       </c>
       <c r="C5" t="n">
-        <v>205.9215809657685</v>
+        <v>200.9637550593221</v>
       </c>
       <c r="D5" t="n">
-        <v>154.2080206445678</v>
+        <v>138.2055330653448</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>49.54978838104078</v>
       </c>
       <c r="C6" t="n">
-        <v>246.6621471966026</v>
+        <v>240.6243988154848</v>
       </c>
       <c r="D6" t="n">
-        <v>78.53098061040662</v>
+        <v>72.93600044390405</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="C7" t="n">
-        <v>186.6066766324167</v>
+        <v>181.0372219062246</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>116.0769398116216</v>
+        <v>108.6500184289945</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>54.0265579124062</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.880447764260142</v>
+        <v>3.493058331710151</v>
       </c>
       <c r="C2" t="n">
-        <v>3.62559427178347</v>
+        <v>4.485605260703677</v>
       </c>
       <c r="D2" t="n">
-        <v>13.02779203535517</v>
+        <v>10.42812411450962</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3131207643925</v>
+        <v>18.32432089976671</v>
       </c>
       <c r="C3" t="n">
-        <v>20.98976591679681</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="D3" t="n">
-        <v>82.32936247813751</v>
+        <v>65.11441648416969</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.43452298901639</v>
+        <v>43.95480821453819</v>
       </c>
       <c r="C4" t="n">
-        <v>68.98250243890213</v>
+        <v>71.79030087304801</v>
       </c>
       <c r="D4" t="n">
-        <v>173.994163875958</v>
+        <v>150.8936403950305</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.1339125695344</v>
+        <v>65.11441648416971</v>
       </c>
       <c r="C5" t="n">
-        <v>195.1468999116598</v>
+        <v>191.1953654020664</v>
       </c>
       <c r="D5" t="n">
-        <v>169.4741974456057</v>
+        <v>154.0362147963246</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.78000036992004</v>
+        <v>58.84792088796232</v>
       </c>
       <c r="C6" t="n">
-        <v>284.1766904712818</v>
+        <v>278.9037235517721</v>
       </c>
       <c r="D6" t="n">
-        <v>94.95365620704727</v>
+        <v>86.74231840872694</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>241.7023577947477</v>
+        <v>238.4684808569587</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>149.3729132011522</v>
+        <v>143.5315143608837</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>61.34843229067891</v>
+        <v>61.01561981893925</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.831180452598554</v>
+        <v>4.287292224445821</v>
       </c>
       <c r="C2" t="n">
-        <v>8.597164646089318</v>
+        <v>11.2037048008646</v>
       </c>
       <c r="D2" t="n">
-        <v>17.96500124001238</v>
+        <v>18.08477445993049</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.73465038241288</v>
+        <v>15.15818455357075</v>
       </c>
       <c r="C3" t="n">
-        <v>17.66164119940012</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="D3" t="n">
-        <v>74.99570712741385</v>
+        <v>59.38591862988956</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.07043345946106</v>
+        <v>39.3219407981975</v>
       </c>
       <c r="C4" t="n">
-        <v>61.4524975473291</v>
+        <v>64.43897406364789</v>
       </c>
       <c r="D4" t="n">
-        <v>174.4663845217007</v>
+        <v>148.9537069314388</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.15845626214058</v>
+        <v>65.38439710283758</v>
       </c>
       <c r="C5" t="n">
-        <v>165.8908183251048</v>
+        <v>165.2772260099505</v>
       </c>
       <c r="D5" t="n">
-        <v>186.5075201142878</v>
+        <v>166.1607989437727</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.3045567436241</v>
+        <v>70.15863618858982</v>
       </c>
       <c r="C6" t="n">
-        <v>295.5276574277834</v>
+        <v>290.1339355406514</v>
       </c>
       <c r="D6" t="n">
-        <v>116.5687954114493</v>
+        <v>107.8744377426395</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.30935800449154</v>
+        <v>37.78845088416398</v>
       </c>
       <c r="C7" t="n">
-        <v>311.4103717870882</v>
+        <v>308.1166082393402</v>
       </c>
       <c r="D7" t="n">
-        <v>57.73069200052944</v>
+        <v>55.81432048183967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>213.5448518892449</v>
+        <v>210.0400125850838</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>106.2781159755342</v>
+        <v>104.8359285979956</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>12.29148125717007</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.776022654711485</v>
+        <v>5.230751768227005</v>
       </c>
       <c r="C2" t="n">
-        <v>5.564545987670921</v>
+        <v>2.526036843027043</v>
       </c>
       <c r="D2" t="n">
-        <v>8.949612071913924</v>
+        <v>6.673920893469817</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.496003574822891</v>
+        <v>3.069925071179776</v>
       </c>
       <c r="C2" t="n">
-        <v>4.951935420220912</v>
+        <v>6.363688618927824</v>
       </c>
       <c r="D2" t="n">
-        <v>13.36649499332032</v>
+        <v>13.30955362647401</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.74647241259284</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="C3" t="n">
-        <v>24.88730430265664</v>
+        <v>29.99730110326129</v>
       </c>
       <c r="D3" t="n">
-        <v>81.53414683769761</v>
+        <v>66.64594290279472</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.67098531701964</v>
+        <v>51.57415214719769</v>
       </c>
       <c r="C4" t="n">
-        <v>90.73017758337748</v>
+        <v>93.71665409969629</v>
       </c>
       <c r="D4" t="n">
-        <v>179.0354383372653</v>
+        <v>152.884624739243</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.19689898685967</v>
+        <v>41.33157834879072</v>
       </c>
       <c r="C5" t="n">
-        <v>249.7320722677824</v>
+        <v>246.5904796141926</v>
       </c>
       <c r="D5" t="n">
-        <v>169.1060420565131</v>
+        <v>153.4471661737765</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.14470212761856</v>
+        <v>23.46671537461151</v>
       </c>
       <c r="C6" t="n">
-        <v>260.1464519144326</v>
+        <v>259.7841870115656</v>
       </c>
       <c r="D6" t="n">
-        <v>90.16370915802707</v>
+        <v>84.81023892676923</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.707300315414209</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>150.135731167352</v>
+        <v>147.6803801590307</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>78.27474445959818</v>
+        <v>77.27336180126643</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>25.61870634232051</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.851036390861743</v>
+        <v>7.192283681312134</v>
       </c>
       <c r="C2" t="n">
-        <v>5.958226817073892</v>
+        <v>2.999239236474005</v>
       </c>
       <c r="D2" t="n">
-        <v>24.40330268446296</v>
+        <v>12.1285111382651</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.39242134425824</v>
+        <v>11.11338401207389</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01935721664445</v>
+        <v>6.464808632465247</v>
       </c>
       <c r="D3" t="n">
-        <v>10.65196259107789</v>
+        <v>9.007535186464485</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39834707538312</v>
+        <v>13.39952731906907</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14428762994692</v>
+        <v>70.15046655277338</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576276126515661</v>
+        <v>1.576414978714008</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.888121819444869</v>
+        <v>4.749695393146069</v>
       </c>
       <c r="C2" t="n">
-        <v>3.426299487821368</v>
+        <v>7.082327938436491</v>
       </c>
       <c r="D2" t="n">
-        <v>28.64347101910494</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.02060100625596</v>
+        <v>19.59568417676634</v>
       </c>
       <c r="C3" t="n">
-        <v>19.78221624057323</v>
+        <v>9.792933349861933</v>
       </c>
       <c r="D3" t="n">
-        <v>28.57376693210342</v>
+        <v>17.01859645311846</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.69363796301277</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C4" t="n">
-        <v>21.91359050649305</v>
+        <v>10.55476956835746</v>
       </c>
       <c r="D4" t="n">
-        <v>20.65008121112741</v>
+        <v>19.79497896072844</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43989716998632</v>
+        <v>15.44670412892146</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13837368518685</v>
+        <v>86.17634935082498</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250504667365542</v>
+        <v>3.251937711351886</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.804493338134643</v>
+        <v>5.852198065015236</v>
       </c>
       <c r="C2" t="n">
-        <v>4.101741908343174</v>
+        <v>4.076216468032757</v>
       </c>
       <c r="D2" t="n">
-        <v>33.20074386221863</v>
+        <v>21.4845667597372</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.14898897133403</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="C3" t="n">
-        <v>15.86995163914969</v>
+        <v>20.56761440397068</v>
       </c>
       <c r="D3" t="n">
-        <v>44.85605260703677</v>
+        <v>34.72441629920969</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.43457974227862</v>
+        <v>27.01867856857647</v>
       </c>
       <c r="C4" t="n">
-        <v>38.17329598422873</v>
+        <v>18.67185958707009</v>
       </c>
       <c r="D4" t="n">
-        <v>30.31146036862027</v>
+        <v>23.68760860806704</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.35806017460961</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>25.37817815478006</v>
+        <v>13.57266201121216</v>
       </c>
       <c r="D5" t="n">
-        <v>30.09056713516474</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73117827343683</v>
+        <v>16.74584481955841</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0601874679646</v>
+        <v>102.1496533993063</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182794568359206</v>
+        <v>5.023753445867524</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.39903153628071</v>
+        <v>5.529203070318036</v>
       </c>
       <c r="C2" t="n">
-        <v>6.844744994008762</v>
+        <v>5.123741268464104</v>
       </c>
       <c r="D2" t="n">
-        <v>30.67176177607885</v>
+        <v>18.90846078379357</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.59844949342983</v>
+        <v>19.36497346626834</v>
       </c>
       <c r="C3" t="n">
-        <v>15.88958659323463</v>
+        <v>17.77945092390974</v>
       </c>
       <c r="D3" t="n">
-        <v>60.1124119310322</v>
+        <v>43.32943492693298</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.2423781764245</v>
+        <v>31.17932533917445</v>
       </c>
       <c r="C4" t="n">
-        <v>39.0283982346277</v>
+        <v>37.31819373382976</v>
       </c>
       <c r="D4" t="n">
-        <v>45.12897846881738</v>
+        <v>34.88051418418493</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.60598467989432</v>
+        <v>26.31083847381452</v>
       </c>
       <c r="C5" t="n">
-        <v>49.75006491270713</v>
+        <v>24.93639168786899</v>
       </c>
       <c r="D5" t="n">
-        <v>33.74757733348411</v>
+        <v>31.857713002809</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.7597749120958</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>26.64659618866693</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>33.30088212805181</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>30.58536797810513</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0536678712099</v>
+        <v>18.08168471036344</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7786903978932</v>
+        <v>117.9614669199901</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017889290403301</v>
+        <v>6.888260842043216</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.128870991163589</v>
+        <v>5.625414345334224</v>
       </c>
       <c r="C2" t="n">
-        <v>7.664504327054848</v>
+        <v>7.101962892521426</v>
       </c>
       <c r="D2" t="n">
-        <v>38.17820472274996</v>
+        <v>23.09266949929347</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.37969968183204</v>
+        <v>17.10204500797944</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69033286700153</v>
+        <v>17.89726064841935</v>
       </c>
       <c r="D3" t="n">
-        <v>65.90472338608838</v>
+        <v>45.21929925760809</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.84825537866502</v>
+        <v>25.29571134762332</v>
       </c>
       <c r="C4" t="n">
-        <v>32.99163160121406</v>
+        <v>34.42105625859742</v>
       </c>
       <c r="D4" t="n">
-        <v>55.90071427981338</v>
+        <v>41.60646770597982</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.35363446217388</v>
+        <v>22.776546738526</v>
       </c>
       <c r="C5" t="n">
-        <v>45.52854978444584</v>
+        <v>36.76645152404306</v>
       </c>
       <c r="D5" t="n">
-        <v>33.64940256305943</v>
+        <v>30.23782929080177</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.73210604992764</v>
+        <v>12.84027822384404</v>
       </c>
       <c r="C6" t="n">
-        <v>36.58875518957439</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="D6" t="n">
-        <v>31.19503330244241</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28348840681585</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
         <v>30.12492830481337</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054977780503388</v>
+        <v>7.072084056733613</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14041669221926</v>
+        <v>67.18479853896932</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409361112814618</v>
+        <v>5.30406304255021</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.193846266093127</v>
+        <v>4.945063186291184</v>
       </c>
       <c r="C2" t="n">
-        <v>5.492878405260903</v>
+        <v>4.277474747403353</v>
       </c>
       <c r="D2" t="n">
-        <v>27.26607899004666</v>
+        <v>32.26710179547992</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.15728492132452</v>
+        <v>18.84955592153876</v>
       </c>
       <c r="C3" t="n">
-        <v>26.65935890882213</v>
+        <v>24.47497026687298</v>
       </c>
       <c r="D3" t="n">
-        <v>82.04956438242718</v>
+        <v>54.17774705886023</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.9488356128547</v>
+        <v>30.57947749187965</v>
       </c>
       <c r="C4" t="n">
-        <v>44.88648678586841</v>
+        <v>41.2618742617892</v>
       </c>
       <c r="D4" t="n">
-        <v>76.93367709559706</v>
+        <v>56.3729349255561</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>32.2749557771139</v>
       </c>
       <c r="C5" t="n">
-        <v>55.0515025156399</v>
+        <v>53.77523050011905</v>
       </c>
       <c r="D5" t="n">
-        <v>47.49204519293946</v>
+        <v>39.04901493641689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.88181472705867</v>
+        <v>23.62772199810799</v>
       </c>
       <c r="C6" t="n">
-        <v>57.68062286761285</v>
+        <v>43.23027840880406</v>
       </c>
       <c r="D6" t="n">
-        <v>35.34095385747668</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.69596131131975</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>38.86640986342697</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>22.78145547704723</v>
+        <v>19.69385894719101</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.275722939350572</v>
+        <v>7.301655738442974</v>
       </c>
       <c r="C21" t="n">
-        <v>75.48562549576218</v>
+        <v>77.58009222095659</v>
       </c>
       <c r="D21" t="n">
-        <v>5.456792204512928</v>
+        <v>6.388948771137602</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.938591862988956</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C2" t="n">
-        <v>8.594219402976577</v>
+        <v>7.368998268076559</v>
       </c>
       <c r="D2" t="n">
-        <v>20.95736824255666</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.07107104980004</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="C3" t="n">
-        <v>23.4539526544563</v>
+        <v>19.59568417676634</v>
       </c>
       <c r="D3" t="n">
-        <v>84.82300164692441</v>
+        <v>68.19219553698345</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.6274853183965</v>
+        <v>34.57420890045992</v>
       </c>
       <c r="C4" t="n">
-        <v>57.77683414262904</v>
+        <v>53.50132289063419</v>
       </c>
       <c r="D4" t="n">
-        <v>100.7744383455266</v>
+        <v>71.68819911180634</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.68777283898307</v>
+        <v>40.05530633326987</v>
       </c>
       <c r="C5" t="n">
-        <v>71.00490270965058</v>
+        <v>67.12699927787567</v>
       </c>
       <c r="D5" t="n">
-        <v>63.91177554646737</v>
+        <v>51.17359908386501</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.91705983342032</v>
+        <v>35.26045054572845</v>
       </c>
       <c r="C6" t="n">
-        <v>74.22405343187586</v>
+        <v>66.89825206278616</v>
       </c>
       <c r="D6" t="n">
-        <v>42.58625191481815</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="C7" t="n">
-        <v>62.82105384704915</v>
+        <v>45.75337000871835</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>38.7201294554942</v>
+        <v>26.36974333606933</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.73593522975338</v>
+        <v>24.73906039931537</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.484381626188242</v>
+        <v>7.520022928966736</v>
       </c>
       <c r="C21" t="n">
-        <v>84.19929329461772</v>
+        <v>87.42026654923831</v>
       </c>
       <c r="D21" t="n">
-        <v>6.548833922914712</v>
+        <v>7.520022928966736</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_12_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497612980262</v>
+        <v>10.84497635853887</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907123660797</v>
+        <v>37.78907203363421</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.844744994008762</v>
+        <v>4.361905049968579</v>
       </c>
       <c r="C2" t="n">
-        <v>8.021860491400687</v>
+        <v>5.818818643070845</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1472875178328</v>
+        <v>25.89457744721387</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66025854106837</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C3" t="n">
-        <v>24.88730430265664</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7636137585841</v>
+        <v>71.2552483742335</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.59973434077034</v>
+        <v>30.57947749187965</v>
       </c>
       <c r="C4" t="n">
-        <v>50.98706702005809</v>
+        <v>76.20620204675016</v>
       </c>
       <c r="D4" t="n">
-        <v>88.07553179109411</v>
+        <v>116.281143334105</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.78027810736052</v>
+        <v>38.75449062514284</v>
       </c>
       <c r="C5" t="n">
-        <v>84.6021084134689</v>
+        <v>148.1457285708437</v>
       </c>
       <c r="D5" t="n">
-        <v>65.40894079544375</v>
+        <v>93.97779898902593</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.24286120251001</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="C6" t="n">
-        <v>87.46684821446109</v>
+        <v>170.9085308415103</v>
       </c>
       <c r="D6" t="n">
-        <v>45.80638438474769</v>
+        <v>60.09572222006002</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>73.12155076000668</v>
+        <v>129.594623951396</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>44.6449768506237</v>
+        <v>72.43334561932966</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.725775451094117</v>
+        <v>7.643711200564502</v>
       </c>
       <c r="C21" t="n">
-        <v>96.57219313867647</v>
+        <v>92.67999830684458</v>
       </c>
       <c r="D21" t="n">
-        <v>8.691497382480883</v>
+        <v>7.643711200564502</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.35329030480861</v>
+        <v>5.014767273292708</v>
       </c>
       <c r="C2" t="n">
-        <v>12.80297181108265</v>
+        <v>5.506622873120359</v>
       </c>
       <c r="D2" t="n">
-        <v>22.78341897245573</v>
+        <v>31.43752498539136</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.99329199698629</v>
+        <v>14.33842522052466</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4706834231575</v>
+        <v>25.47635292520473</v>
       </c>
       <c r="D3" t="n">
-        <v>77.6120647592316</v>
+        <v>74.02868563873074</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3362250454047</v>
+        <v>28.38428962518378</v>
       </c>
       <c r="C4" t="n">
-        <v>56.28359588446964</v>
+        <v>73.02828472810323</v>
       </c>
       <c r="D4" t="n">
-        <v>103.3142196564131</v>
+        <v>122.2158082062769</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.30827844579606</v>
+        <v>41.57701527485243</v>
       </c>
       <c r="C5" t="n">
-        <v>89.41267216427826</v>
+        <v>142.9179220457295</v>
       </c>
       <c r="D5" t="n">
-        <v>79.74245727744719</v>
+        <v>111.0111216577081</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.13847715069036</v>
+        <v>42.54600025894403</v>
       </c>
       <c r="C6" t="n">
-        <v>109.8065172245973</v>
+        <v>200.4129945972397</v>
       </c>
       <c r="D6" t="n">
-        <v>55.18502020341747</v>
+        <v>72.25172229404403</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.23813239043802</v>
+        <v>31.4404702285041</v>
       </c>
       <c r="C7" t="n">
-        <v>99.89086541170445</v>
+        <v>180.7976754663884</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>48.56804067679396</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.03456645829366</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>116.9114253602314</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48905889209769</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>36.15776794741003</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.917478164567607</v>
+        <v>7.812790316002913</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8962704510917</v>
+        <v>100.5896753185375</v>
       </c>
       <c r="D21" t="n">
-        <v>9.896847705709508</v>
+        <v>8.789389105503277</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.008516934168732</v>
+        <v>5.406484607287184</v>
       </c>
       <c r="C2" t="n">
-        <v>12.90900056314131</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="D2" t="n">
-        <v>27.58416524622263</v>
+        <v>38.67693255650734</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.98133109808609</v>
+        <v>15.0354660905399</v>
       </c>
       <c r="C3" t="n">
-        <v>38.79376053331271</v>
+        <v>23.40977400776519</v>
       </c>
       <c r="D3" t="n">
-        <v>77.16536955379929</v>
+        <v>79.26630964088747</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.03366682604742</v>
+        <v>27.14630577012855</v>
       </c>
       <c r="C4" t="n">
-        <v>62.74153228300516</v>
+        <v>67.99977298695107</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3029217100476</v>
+        <v>128.6099310040364</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.5291716792516</v>
+        <v>41.62610266006477</v>
       </c>
       <c r="C5" t="n">
-        <v>96.03946916794425</v>
+        <v>138.9418438435299</v>
       </c>
       <c r="D5" t="n">
-        <v>95.57313900842701</v>
+        <v>123.2338805755809</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.37748381117885</v>
+        <v>48.1409804254466</v>
       </c>
       <c r="C6" t="n">
-        <v>123.572583533546</v>
+        <v>209.7916304159094</v>
       </c>
       <c r="D6" t="n">
-        <v>64.76491430145784</v>
+        <v>86.05804025886691</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.76010337392783</v>
+        <v>38.74663664350886</v>
       </c>
       <c r="C7" t="n">
-        <v>127.1991595530337</v>
+        <v>223.7962614169901</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>55.095681162331</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.71459882216722</v>
+        <v>23.699389580518</v>
       </c>
       <c r="C8" t="n">
-        <v>97.71825774220626</v>
+        <v>165.979175618487</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.86093598336221</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>62.23593221531803</v>
+        <v>94.2968669929061</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>36.86953503298896</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.32797015314322</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.094232633200704</v>
+        <v>7.966089234260981</v>
       </c>
       <c r="C21" t="n">
-        <v>114.3310359439599</v>
+        <v>107.5422046625232</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12956987065097</v>
+        <v>9.957611542826227</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.078801858247003</v>
+        <v>5.022621254926682</v>
       </c>
       <c r="C2" t="n">
-        <v>8.46757394912874</v>
+        <v>4.888121819444869</v>
       </c>
       <c r="D2" t="n">
-        <v>22.4388255282651</v>
+        <v>31.70161511783375</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.89850443803086</v>
+        <v>18.24578108342697</v>
       </c>
       <c r="C3" t="n">
-        <v>55.80253950938871</v>
+        <v>37.42422248588841</v>
       </c>
       <c r="D3" t="n">
-        <v>85.29914928348413</v>
+        <v>87.48353792543327</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.78971036930871</v>
+        <v>19.99918248321178</v>
       </c>
       <c r="C4" t="n">
-        <v>84.08080038251383</v>
+        <v>105.2541531200048</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5807152526205</v>
+        <v>128.2398121195353</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.01755795215198</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C5" t="n">
-        <v>73.82742735936016</v>
+        <v>125.3446381397115</v>
       </c>
       <c r="D5" t="n">
-        <v>65.2862223324129</v>
+        <v>84.52847733565038</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.76484788153306</v>
+        <v>24.03023855684918</v>
       </c>
       <c r="C6" t="n">
-        <v>83.76369587404213</v>
+        <v>147.4015638110246</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>36.26674194258143</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="C7" t="n">
-        <v>68.68994162303657</v>
+        <v>116.719002810199</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>45.8132566186774</v>
+        <v>69.5126461991954</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>27.61656292046278</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.72062817711293</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.043237956715865</v>
+        <v>3.065998080362789</v>
       </c>
       <c r="C2" t="n">
-        <v>3.749294482518569</v>
+        <v>2.363066724122073</v>
       </c>
       <c r="D2" t="n">
-        <v>15.97303514809561</v>
+        <v>21.7614196123348</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.69019399828129</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C3" t="n">
-        <v>44.73333414400592</v>
+        <v>28.81429511964389</v>
       </c>
       <c r="D3" t="n">
-        <v>84.94081137143404</v>
+        <v>92.94205516104554</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>26.27844079957437</v>
       </c>
       <c r="C4" t="n">
-        <v>114.0349045867883</v>
+        <v>103.5184231788964</v>
       </c>
       <c r="D4" t="n">
-        <v>124.5258605543697</v>
+        <v>141.0791085956752</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.23278168356029</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="C5" t="n">
-        <v>113.7845589222053</v>
+        <v>159.0676717805895</v>
       </c>
       <c r="D5" t="n">
-        <v>84.72482687649975</v>
+        <v>102.2490233973053</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="C6" t="n">
-        <v>102.4404641996334</v>
+        <v>173.9676566879433</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>45.72588107299945</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.73883941513712</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>89.88980154854221</v>
+        <v>153.0701750553457</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>61.83537915198535</v>
+        <v>93.12858722485242</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.414739499548659</v>
+        <v>3.561780671007428</v>
       </c>
       <c r="C2" t="n">
-        <v>5.542947538177491</v>
+        <v>11.44423298840507</v>
       </c>
       <c r="D2" t="n">
-        <v>15.74919667152733</v>
+        <v>21.54739861280899</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.32003405605123</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="C3" t="n">
-        <v>28.27924262082937</v>
+        <v>18.55503161026472</v>
       </c>
       <c r="D3" t="n">
-        <v>78.36310175298041</v>
+        <v>88.85307597285758</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.49084246105696</v>
+        <v>30.04344324536089</v>
       </c>
       <c r="C4" t="n">
-        <v>112.8096834518882</v>
+        <v>87.6288365856618</v>
       </c>
       <c r="D4" t="n">
-        <v>137.3779197506647</v>
+        <v>153.190930022968</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.89041377668541</v>
+        <v>34.31208226342603</v>
       </c>
       <c r="C5" t="n">
-        <v>164.1482161500667</v>
+        <v>175.7082953675729</v>
       </c>
       <c r="D5" t="n">
-        <v>107.4031988446011</v>
+        <v>125.0992012136498</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.88059629964295</v>
+        <v>33.89189424600839</v>
       </c>
       <c r="C6" t="n">
-        <v>140.1965174095573</v>
+        <v>209.8721337276577</v>
       </c>
       <c r="D6" t="n">
-        <v>54.17872880656449</v>
+        <v>62.67182819600364</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.45854259780804</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>118.874920768725</v>
+        <v>199.0630915039002</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>89.12305659152544</v>
+        <v>141.0280577150543</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>71.77655640518853</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.741440500884595</v>
+        <v>2.110757564130642</v>
       </c>
       <c r="C2" t="n">
-        <v>2.533890824661018</v>
+        <v>5.434955290710342</v>
       </c>
       <c r="D2" t="n">
-        <v>10.90034476025234</v>
+        <v>15.02761210890593</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.86137795171873</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="C3" t="n">
-        <v>27.12568906833937</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D3" t="n">
-        <v>76.52232480751763</v>
+        <v>88.82362354173017</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.41725244096745</v>
+        <v>32.86400439966198</v>
       </c>
       <c r="C4" t="n">
-        <v>107.7045953898048</v>
+        <v>82.57479940419921</v>
       </c>
       <c r="D4" t="n">
-        <v>146.1586712174481</v>
+        <v>163.2351907851172</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.49204519293946</v>
+        <v>35.9074222828271</v>
       </c>
       <c r="C5" t="n">
-        <v>199.8838325846506</v>
+        <v>203.0499689308466</v>
       </c>
       <c r="D5" t="n">
-        <v>116.4843651088841</v>
+        <v>131.4805612912541</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>26.96860943565989</v>
       </c>
       <c r="C6" t="n">
-        <v>174.2494182790622</v>
+        <v>246.9036571318474</v>
       </c>
       <c r="D6" t="n">
-        <v>53.29319237733387</v>
+        <v>60.65924540229769</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>122.3483441463502</v>
+        <v>198.1647923545144</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="C8" t="n">
-        <v>69.84644041863932</v>
+        <v>94.29686699290613</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>28.39999758845172</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>19.36890045708532</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.182646130718912</v>
+        <v>2.680171232593792</v>
       </c>
       <c r="C2" t="n">
-        <v>6.842781498600268</v>
+        <v>7.17461222263569</v>
       </c>
       <c r="D2" t="n">
-        <v>14.42972775701962</v>
+        <v>14.53575650907827</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.48140053244621</v>
+        <v>11.16247139728623</v>
       </c>
       <c r="C3" t="n">
-        <v>17.92671307954676</v>
+        <v>25.9770442543706</v>
       </c>
       <c r="D3" t="n">
-        <v>68.38363633931158</v>
+        <v>81.2445312649448</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.65599705954867</v>
+        <v>30.60500293219007</v>
       </c>
       <c r="C4" t="n">
-        <v>88.29249803373266</v>
+        <v>80.37961153750335</v>
       </c>
       <c r="D4" t="n">
-        <v>150.3320807082013</v>
+        <v>168.672109571236</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.3466487217197</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="C5" t="n">
-        <v>200.9637550593221</v>
+        <v>181.6478689782661</v>
       </c>
       <c r="D5" t="n">
-        <v>138.2055330653448</v>
+        <v>153.7416904850505</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.54978838104078</v>
+        <v>35.30070220160257</v>
       </c>
       <c r="C6" t="n">
-        <v>240.6243988154848</v>
+        <v>281.8420944305828</v>
       </c>
       <c r="D6" t="n">
-        <v>72.93600044390405</v>
+        <v>81.26809320984674</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.27781890476862</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>181.0372219062246</v>
+        <v>264.638929409066</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>108.6500184289945</v>
+        <v>160.2212253330794</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>60.4609323660398</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.493058331710151</v>
+        <v>1.693514789825748</v>
       </c>
       <c r="C2" t="n">
-        <v>4.485605260703677</v>
+        <v>4.689808783187013</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42812411450962</v>
+        <v>10.4507043117073</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32432089976671</v>
+        <v>10.39670818797372</v>
       </c>
       <c r="C3" t="n">
-        <v>22.39857387239098</v>
+        <v>27.05205799052086</v>
       </c>
       <c r="D3" t="n">
-        <v>65.11441648416969</v>
+        <v>75.99218104722436</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.95480821453819</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C4" t="n">
-        <v>71.79030087304801</v>
+        <v>75.9637103638012</v>
       </c>
       <c r="D4" t="n">
-        <v>150.8936403950305</v>
+        <v>170.4716531131204</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.11441648416971</v>
+        <v>44.44862730977434</v>
       </c>
       <c r="C5" t="n">
-        <v>191.1953654020664</v>
+        <v>173.7447999590793</v>
       </c>
       <c r="D5" t="n">
-        <v>154.0362147963246</v>
+        <v>170.0141586829414</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.84792088796232</v>
+        <v>41.0164373357275</v>
       </c>
       <c r="C6" t="n">
-        <v>278.9037235517721</v>
+        <v>301.3238958736566</v>
       </c>
       <c r="D6" t="n">
-        <v>86.74231840872694</v>
+        <v>94.99390786292139</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>238.4684808569587</v>
+        <v>314.9436817746725</v>
       </c>
       <c r="D7" t="n">
-        <v>45.6934833987593</v>
+        <v>47.31042186765379</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>143.5315143608837</v>
+        <v>209.1220784816131</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>61.01561981893925</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.287292224445821</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C2" t="n">
-        <v>11.2037048008646</v>
+        <v>19.01056254503524</v>
       </c>
       <c r="D2" t="n">
-        <v>18.08477445993049</v>
+        <v>11.29893432817654</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15818455357075</v>
+        <v>8.192684591939633</v>
       </c>
       <c r="C3" t="n">
-        <v>19.90002596508285</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D3" t="n">
-        <v>59.38591862988956</v>
+        <v>69.0070461315083</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C4" t="n">
-        <v>64.43897406364789</v>
+        <v>72.05831799630738</v>
       </c>
       <c r="D4" t="n">
-        <v>148.9537069314388</v>
+        <v>167.2937357944735</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.38439710283758</v>
+        <v>43.29507375728434</v>
       </c>
       <c r="C5" t="n">
-        <v>165.2772260099505</v>
+        <v>159.2394776288327</v>
       </c>
       <c r="D5" t="n">
-        <v>166.1607989437727</v>
+        <v>186.0411899547706</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.15863618858982</v>
+        <v>47.85921883432777</v>
       </c>
       <c r="C6" t="n">
-        <v>290.1339355406514</v>
+        <v>292.7100415165951</v>
       </c>
       <c r="D6" t="n">
-        <v>107.8744377426395</v>
+        <v>116.6895503790716</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.78845088416398</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>308.1166082393402</v>
+        <v>363.1524027917121</v>
       </c>
       <c r="D7" t="n">
-        <v>55.81432048183967</v>
+        <v>57.85046522044755</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>210.0400125850838</v>
+        <v>289.8168310321796</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>104.8359285979956</v>
+        <v>133.7906136393468</v>
       </c>
       <c r="D9" t="n">
-        <v>34.83437204208531</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
         <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.230751768227005</v>
+        <v>4.094869674413446</v>
       </c>
       <c r="C2" t="n">
-        <v>2.526036843027043</v>
+        <v>5.378995671568275</v>
       </c>
       <c r="D2" t="n">
-        <v>6.673920893469817</v>
+        <v>22.71371488545421</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.069925071179776</v>
+        <v>1.723948968657399</v>
       </c>
       <c r="C2" t="n">
-        <v>6.363688618927824</v>
+        <v>11.10160303962293</v>
       </c>
       <c r="D2" t="n">
-        <v>13.30955362647401</v>
+        <v>8.405723843761191</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.56623174563893</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C3" t="n">
-        <v>29.99730110326129</v>
+        <v>40.50200153870216</v>
       </c>
       <c r="D3" t="n">
-        <v>66.64594290279472</v>
+        <v>73.7341613274567</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.57415214719769</v>
+        <v>32.92781800043802</v>
       </c>
       <c r="C4" t="n">
-        <v>93.71665409969629</v>
+        <v>101.3359980323558</v>
       </c>
       <c r="D4" t="n">
-        <v>152.884624739243</v>
+        <v>172.5775019387298</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.33157834879072</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="C5" t="n">
-        <v>246.5904796141926</v>
+        <v>242.5653140267807</v>
       </c>
       <c r="D5" t="n">
-        <v>153.4471661737765</v>
+        <v>169.4987411382118</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.46671537461151</v>
+        <v>15.13462260866883</v>
       </c>
       <c r="C6" t="n">
-        <v>259.7841870115656</v>
+        <v>293.6760812575739</v>
       </c>
       <c r="D6" t="n">
-        <v>84.81023892676923</v>
+        <v>89.1574177611741</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>147.6803801590307</v>
+        <v>203.7941336906656</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>77.27336180126643</v>
+        <v>98.55274329081605</v>
       </c>
       <c r="D8" t="n">
-        <v>25.61870634232051</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
         <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.192283681312134</v>
+        <v>5.69708192774424</v>
       </c>
       <c r="C2" t="n">
-        <v>2.999239236474005</v>
+        <v>8.505862109594364</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1285111382651</v>
+        <v>33.91251094779757</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.11338401207389</v>
+        <v>8.70810213666921</v>
       </c>
       <c r="C3" t="n">
-        <v>6.464808632465247</v>
+        <v>13.55302705712722</v>
       </c>
       <c r="D3" t="n">
-        <v>9.007535186464485</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39952731906907</v>
+        <v>13.39647919431755</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15046655277338</v>
+        <v>70.13450872319189</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576414978714008</v>
+        <v>1.576056375802065</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.749695393146069</v>
+        <v>4.53371089821177</v>
       </c>
       <c r="C2" t="n">
-        <v>7.082327938436491</v>
+        <v>11.04367992507237</v>
       </c>
       <c r="D2" t="n">
-        <v>27.06874770149305</v>
+        <v>27.57434776918016</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.59568417676634</v>
+        <v>15.25635932399543</v>
       </c>
       <c r="C3" t="n">
-        <v>9.792933349861933</v>
+        <v>25.82487336021235</v>
       </c>
       <c r="D3" t="n">
-        <v>17.01859645311846</v>
+        <v>45.33220024359647</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.97968639784708</v>
+        <v>10.27398972494287</v>
       </c>
       <c r="C4" t="n">
-        <v>10.55476956835746</v>
+        <v>21.21164089795658</v>
       </c>
       <c r="D4" t="n">
-        <v>19.79497896072844</v>
+        <v>26.71237328485147</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44670412892146</v>
+        <v>15.43504081685015</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17634935082498</v>
+        <v>86.11128034663768</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251937711351886</v>
+        <v>3.249482277231611</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.852198065015236</v>
+        <v>5.036365722786137</v>
       </c>
       <c r="C2" t="n">
-        <v>4.076216468032757</v>
+        <v>9.967684441217866</v>
       </c>
       <c r="D2" t="n">
-        <v>21.4845667597372</v>
+        <v>31.10176727053895</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01016163440774</v>
+        <v>15.64414966717292</v>
       </c>
       <c r="C3" t="n">
-        <v>20.56761440397068</v>
+        <v>36.03014074585794</v>
       </c>
       <c r="D3" t="n">
-        <v>34.72441629920969</v>
+        <v>56.87264450701772</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.01867856857647</v>
+        <v>20.85428473361074</v>
       </c>
       <c r="C4" t="n">
-        <v>18.67185958707009</v>
+        <v>46.34143688356219</v>
       </c>
       <c r="D4" t="n">
-        <v>23.68760860806704</v>
+        <v>43.39324852770901</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.73188506574938</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="C5" t="n">
-        <v>13.57266201121216</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>29.91876128692155</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74584481955841</v>
+        <v>16.72210103500493</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1496533993063</v>
+        <v>102.0048163135301</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023753445867524</v>
+        <v>4.180525258751232</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.529203070318036</v>
+        <v>4.80761850769663</v>
       </c>
       <c r="C2" t="n">
-        <v>5.123741268464104</v>
+        <v>12.00382917982575</v>
       </c>
       <c r="D2" t="n">
-        <v>18.90846078379357</v>
+        <v>28.41374205631119</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.36497346626834</v>
+        <v>16.46390900021901</v>
       </c>
       <c r="C3" t="n">
-        <v>17.77945092390974</v>
+        <v>37.49294482518569</v>
       </c>
       <c r="D3" t="n">
-        <v>43.32943492693298</v>
+        <v>67.85840131753953</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.17932533917445</v>
+        <v>25.88279647476291</v>
       </c>
       <c r="C4" t="n">
-        <v>37.31819373382976</v>
+        <v>70.36087621566466</v>
       </c>
       <c r="D4" t="n">
-        <v>34.88051418418493</v>
+        <v>61.12066682329367</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.31083847381452</v>
+        <v>20.00310947402876</v>
       </c>
       <c r="C5" t="n">
-        <v>24.93639168786899</v>
+        <v>56.52412407201012</v>
       </c>
       <c r="D5" t="n">
-        <v>31.857713002809</v>
+        <v>39.785325714602</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>17.26796036999715</v>
+        <v>25.92206638293279</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.04286240828414</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.40016181936776</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08168471036344</v>
+        <v>18.03670225542043</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9614669199901</v>
+        <v>117.6680099520285</v>
       </c>
       <c r="D21" t="n">
-        <v>6.888260842043216</v>
+        <v>6.012234085140141</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.625414345334224</v>
+        <v>5.914048170382785</v>
       </c>
       <c r="C2" t="n">
-        <v>7.101962892521426</v>
+        <v>8.338964999872408</v>
       </c>
       <c r="D2" t="n">
-        <v>23.09266949929347</v>
+        <v>24.08030768976576</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10204500797944</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C3" t="n">
-        <v>17.89726064841935</v>
+        <v>39.98658399397259</v>
       </c>
       <c r="D3" t="n">
-        <v>45.21929925760809</v>
+        <v>70.56802498126073</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.29571134762332</v>
+        <v>21.00743737547325</v>
       </c>
       <c r="C4" t="n">
-        <v>34.42105625859742</v>
+        <v>69.56958756604172</v>
       </c>
       <c r="D4" t="n">
-        <v>41.60646770597982</v>
+        <v>68.47199363269378</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.776546738526</v>
+        <v>17.9905266803228</v>
       </c>
       <c r="C5" t="n">
-        <v>36.76645152404306</v>
+        <v>70.61220362795184</v>
       </c>
       <c r="D5" t="n">
-        <v>30.23782929080177</v>
+        <v>42.11697651218817</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.84027822384404</v>
+        <v>9.740900721536855</v>
       </c>
       <c r="C6" t="n">
-        <v>19.80381469006666</v>
+        <v>39.00385454202154</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>14.85187926984575</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.072084056733613</v>
+        <v>7.043900814260399</v>
       </c>
       <c r="C21" t="n">
-        <v>67.18479853896932</v>
+        <v>66.03657013369124</v>
       </c>
       <c r="D21" t="n">
-        <v>5.30406304255021</v>
+        <v>4.40243800891275</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.945063186291184</v>
+        <v>4.28434698133308</v>
       </c>
       <c r="C2" t="n">
-        <v>4.277474747403353</v>
+        <v>5.076617378660257</v>
       </c>
       <c r="D2" t="n">
-        <v>32.26710179547992</v>
+        <v>21.01038261858599</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.84955592153876</v>
+        <v>18.14760631300229</v>
       </c>
       <c r="C3" t="n">
-        <v>24.47497026687298</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D3" t="n">
-        <v>54.17774705886023</v>
+        <v>73.74397880449916</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="C4" t="n">
-        <v>41.2618742617892</v>
+        <v>87.59054842519618</v>
       </c>
       <c r="D4" t="n">
-        <v>56.3729349255561</v>
+        <v>89.5687700492535</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.2749557771139</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>53.77523050011905</v>
+        <v>105.513334513926</v>
       </c>
       <c r="D5" t="n">
-        <v>39.04901493641689</v>
+        <v>57.60404654668161</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.62772199810799</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>43.23027840880406</v>
+        <v>81.26809320984674</v>
       </c>
       <c r="D6" t="n">
-        <v>33.85164259013428</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.25868267230242</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>23.2360046641135</v>
+        <v>40.36357511240336</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>19.69385894719101</v>
+        <v>22.5311098124643</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.301655738442974</v>
+        <v>7.25837863141702</v>
       </c>
       <c r="C21" t="n">
-        <v>77.58009222095659</v>
+        <v>75.3056783009516</v>
       </c>
       <c r="D21" t="n">
-        <v>6.388948771137602</v>
+        <v>5.443783973562765</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.551382356888213</v>
+        <v>3.651119712093887</v>
       </c>
       <c r="C2" t="n">
-        <v>7.368998268076559</v>
+        <v>7.948229413582177</v>
       </c>
       <c r="D2" t="n">
-        <v>27.29062268265283</v>
+        <v>18.82010349041136</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95616551067416</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C3" t="n">
-        <v>19.59568417676634</v>
+        <v>26.1488501026138</v>
       </c>
       <c r="D3" t="n">
-        <v>68.19219553698345</v>
+        <v>73.30710107610933</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.57420890045992</v>
+        <v>30.57947749187965</v>
       </c>
       <c r="C4" t="n">
-        <v>53.50132289063419</v>
+        <v>88.07553179109411</v>
       </c>
       <c r="D4" t="n">
-        <v>71.68819911180634</v>
+        <v>104.6160171122444</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.05530633326987</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="C5" t="n">
-        <v>67.12699927787567</v>
+        <v>136.5365619681252</v>
       </c>
       <c r="D5" t="n">
-        <v>51.17359908386501</v>
+        <v>76.74812677949441</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.26045054572845</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="C6" t="n">
-        <v>66.89825206278616</v>
+        <v>126.269444477112</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>48.06047711369836</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.72076704583318</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>45.75337000871835</v>
+        <v>81.38590293435632</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>26.36974333606933</v>
+        <v>38.97047512007713</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.73906039931537</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.520022928966736</v>
+        <v>7.458637743942387</v>
       </c>
       <c r="C21" t="n">
-        <v>87.42026654923831</v>
+        <v>83.90967461935186</v>
       </c>
       <c r="D21" t="n">
-        <v>7.520022928966736</v>
+        <v>6.526308025949588</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_12_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_12_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635853887</v>
+        <v>10.84497654683238</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907203363421</v>
+        <v>37.78907268973864</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.361905049968579</v>
+        <v>1.670934592628071</v>
       </c>
       <c r="C2" t="n">
-        <v>5.818818643070845</v>
+        <v>3.802308858547897</v>
       </c>
       <c r="D2" t="n">
-        <v>25.89457744721387</v>
+        <v>22.11092179504666</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16661937228147</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="C3" t="n">
-        <v>28.57867567062465</v>
+        <v>33.84575210390879</v>
       </c>
       <c r="D3" t="n">
-        <v>71.2552483742335</v>
+        <v>88.24439239622455</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>17.47216389248048</v>
       </c>
       <c r="C4" t="n">
-        <v>76.20620204675016</v>
+        <v>112.4523272875424</v>
       </c>
       <c r="D4" t="n">
-        <v>116.281143334105</v>
+        <v>94.96740067490671</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.75449062514284</v>
+        <v>14.72621556370216</v>
       </c>
       <c r="C5" t="n">
-        <v>148.1457285708437</v>
+        <v>153.520797251595</v>
       </c>
       <c r="D5" t="n">
-        <v>93.97779898902593</v>
+        <v>52.44987109938586</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.22019888985433</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>170.9085308415103</v>
+        <v>97.00649065662735</v>
       </c>
       <c r="D6" t="n">
-        <v>60.09572222006002</v>
+        <v>29.94723197034471</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>129.594623951396</v>
+        <v>46.11268966847268</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>72.43334561932966</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.643711200564502</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.67999830684458</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.643711200564502</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.014767273292708</v>
+        <v>1.126064616771091</v>
       </c>
       <c r="C2" t="n">
-        <v>5.506622873120359</v>
+        <v>4.126285600949344</v>
       </c>
       <c r="D2" t="n">
-        <v>31.43752498539136</v>
+        <v>23.13586639828033</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.33842522052466</v>
+        <v>9.032078879070657</v>
       </c>
       <c r="C3" t="n">
-        <v>25.47635292520473</v>
+        <v>22.98271375641783</v>
       </c>
       <c r="D3" t="n">
-        <v>74.02868563873074</v>
+        <v>86.26617077216723</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>20.9436237746972</v>
       </c>
       <c r="C4" t="n">
-        <v>73.02828472810323</v>
+        <v>98.27294519510572</v>
       </c>
       <c r="D4" t="n">
-        <v>122.2158082062769</v>
+        <v>115.3111766023091</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.57701527485243</v>
+        <v>20.15037162966578</v>
       </c>
       <c r="C5" t="n">
-        <v>142.9179220457295</v>
+        <v>181.6233252856599</v>
       </c>
       <c r="D5" t="n">
-        <v>111.0111216577081</v>
+        <v>72.08482518432207</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.54600025894403</v>
+        <v>14.69185439405352</v>
       </c>
       <c r="C6" t="n">
-        <v>200.4129945972397</v>
+        <v>171.2305440885032</v>
       </c>
       <c r="D6" t="n">
-        <v>72.25172229404403</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.4404702285041</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>180.7976754663884</v>
+        <v>91.74628645727292</v>
       </c>
       <c r="D7" t="n">
-        <v>48.56804067679396</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>116.9114253602314</v>
+        <v>44.47807974090174</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>44.53403936004381</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.812790316002913</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.5896753185375</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.789389105503277</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.406484607287184</v>
+        <v>0.6165375582669969</v>
       </c>
       <c r="C2" t="n">
-        <v>7.024404823885929</v>
+        <v>1.802488784997144</v>
       </c>
       <c r="D2" t="n">
-        <v>38.67693255650734</v>
+        <v>15.74821492382308</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.0354660905399</v>
+        <v>7.824529202847079</v>
       </c>
       <c r="C3" t="n">
-        <v>23.40977400776519</v>
+        <v>21.26956401250715</v>
       </c>
       <c r="D3" t="n">
-        <v>79.26630964088747</v>
+        <v>87.5866214343792</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.14630577012855</v>
+        <v>22.8835572382889</v>
       </c>
       <c r="C4" t="n">
-        <v>67.99977298695107</v>
+        <v>91.61080527408686</v>
       </c>
       <c r="D4" t="n">
-        <v>128.6099310040364</v>
+        <v>128.8396599668302</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.62610266006477</v>
+        <v>19.83130362578557</v>
       </c>
       <c r="C5" t="n">
-        <v>138.9418438435299</v>
+        <v>207.860532681656</v>
       </c>
       <c r="D5" t="n">
-        <v>123.2338805755809</v>
+        <v>82.1231954602457</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.1409804254466</v>
+        <v>11.75348351524281</v>
       </c>
       <c r="C6" t="n">
-        <v>209.7916304159094</v>
+        <v>207.6985443104552</v>
       </c>
       <c r="D6" t="n">
-        <v>86.05804025886691</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.74663664350886</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>223.7962614169901</v>
+        <v>84.44012004226816</v>
       </c>
       <c r="D7" t="n">
-        <v>55.095681162331</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.699389580518</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>165.979175618487</v>
+        <v>40.13875488813084</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80772598535042</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>94.2968669929061</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.53926689373453</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>38.52377991464484</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.966089234260981</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5422046625232</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.957611542826227</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.022621254926682</v>
+        <v>1.119192382841364</v>
       </c>
       <c r="C2" t="n">
-        <v>4.888121819444869</v>
+        <v>7.532950134685777</v>
       </c>
       <c r="D2" t="n">
-        <v>31.70161511783375</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24578108342697</v>
+        <v>4.948008429403925</v>
       </c>
       <c r="C3" t="n">
-        <v>37.42422248588841</v>
+        <v>13.62174939642449</v>
       </c>
       <c r="D3" t="n">
-        <v>87.48353792543327</v>
+        <v>81.12672154043518</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.99918248321178</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C4" t="n">
-        <v>105.2541531200048</v>
+        <v>72.45396232111885</v>
       </c>
       <c r="D4" t="n">
-        <v>128.2398121195353</v>
+        <v>141.0535831553647</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.12078032981814</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="C5" t="n">
-        <v>125.3446381397115</v>
+        <v>190.6063167795183</v>
       </c>
       <c r="D5" t="n">
-        <v>84.52847733565038</v>
+        <v>105.0470043544087</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.03023855684918</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>147.4015638110246</v>
+        <v>266.5464651984176</v>
       </c>
       <c r="D6" t="n">
-        <v>36.26674194258143</v>
+        <v>51.92463607761381</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.69029180927252</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>116.719002810199</v>
+        <v>180.6779022464702</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>69.5126461991954</v>
+        <v>70.51402885752715</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>26.95781021091316</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>27.72062817711293</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.065998080362789</v>
+        <v>0.5792311455056182</v>
       </c>
       <c r="C2" t="n">
-        <v>2.363066724122073</v>
+        <v>4.548437113775472</v>
       </c>
       <c r="D2" t="n">
-        <v>21.7614196123348</v>
+        <v>14.37671338099029</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25068982194821</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C3" t="n">
-        <v>28.81429511964389</v>
+        <v>21.6524456171634</v>
       </c>
       <c r="D3" t="n">
-        <v>92.94205516104554</v>
+        <v>78.77052705024283</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.27844079957437</v>
+        <v>15.97892563432108</v>
       </c>
       <c r="C4" t="n">
-        <v>103.5184231788964</v>
+        <v>56.33464676509047</v>
       </c>
       <c r="D4" t="n">
-        <v>141.0791085956752</v>
+        <v>148.1751810019711</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.89421759431538</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>159.0676717805895</v>
+        <v>173.7693436516855</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2490233973053</v>
+        <v>124.6083273615264</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>22.29941735426205</v>
       </c>
       <c r="C6" t="n">
-        <v>173.9676566879433</v>
+        <v>295.6886640512799</v>
       </c>
       <c r="D6" t="n">
-        <v>45.72588107299945</v>
+        <v>64.36239774271665</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>153.0701750553457</v>
+        <v>250.0864831890155</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>93.12858722485242</v>
+        <v>109.4010554227433</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>44.92968368485526</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.561780671007428</v>
+        <v>1.108393158094649</v>
       </c>
       <c r="C2" t="n">
-        <v>11.44423298840507</v>
+        <v>6.803511590430396</v>
       </c>
       <c r="D2" t="n">
-        <v>21.54739861280899</v>
+        <v>14.2049075327471</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.35315143608837</v>
+        <v>3.288854809226815</v>
       </c>
       <c r="C3" t="n">
-        <v>18.55503161026472</v>
+        <v>19.74785507092459</v>
       </c>
       <c r="D3" t="n">
-        <v>88.85307597285758</v>
+        <v>72.71805245356124</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.04344324536089</v>
+        <v>12.50746575210436</v>
       </c>
       <c r="C4" t="n">
-        <v>87.6288365856618</v>
+        <v>55.13495107050087</v>
       </c>
       <c r="D4" t="n">
-        <v>153.190930022968</v>
+        <v>152.3613532128795</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.31208226342603</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C5" t="n">
-        <v>175.7082953675729</v>
+        <v>141.8870869562703</v>
       </c>
       <c r="D5" t="n">
-        <v>125.0992012136498</v>
+        <v>143.8996697499763</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.89189424600839</v>
+        <v>28.69943063824701</v>
       </c>
       <c r="C6" t="n">
-        <v>209.8721337276577</v>
+        <v>288.6043726174349</v>
       </c>
       <c r="D6" t="n">
-        <v>62.67182819600364</v>
+        <v>82.31463626257383</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>14.61233283000952</v>
       </c>
       <c r="C7" t="n">
-        <v>199.0630915039002</v>
+        <v>328.6577154552962</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>46.53189593818607</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>141.0280577150543</v>
+        <v>199.4420461177395</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>71.77655640518853</v>
+        <v>79.76405572694058</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.110757564130642</v>
+        <v>0.7706719478337462</v>
       </c>
       <c r="C2" t="n">
-        <v>5.434955290710342</v>
+        <v>3.700207097306228</v>
       </c>
       <c r="D2" t="n">
-        <v>15.02761210890593</v>
+        <v>10.34074856883165</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.74585051778709</v>
+        <v>4.810563750809371</v>
       </c>
       <c r="C3" t="n">
-        <v>30.69925071179776</v>
+        <v>25.01002276568749</v>
       </c>
       <c r="D3" t="n">
-        <v>88.82362354173017</v>
+        <v>78.29437941368313</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.86400439966198</v>
+        <v>19.29723287467531</v>
       </c>
       <c r="C4" t="n">
-        <v>82.57479940419921</v>
+        <v>81.06879842588461</v>
       </c>
       <c r="D4" t="n">
-        <v>163.2351907851172</v>
+        <v>154.7224564415931</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.9074222828271</v>
+        <v>17.40147805777472</v>
       </c>
       <c r="C5" t="n">
-        <v>203.0499689308466</v>
+        <v>228.1336227743526</v>
       </c>
       <c r="D5" t="n">
-        <v>131.4805612912541</v>
+        <v>129.0752794158494</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.96860943565989</v>
+        <v>9.056622571676828</v>
       </c>
       <c r="C6" t="n">
-        <v>246.9036571318474</v>
+        <v>281.5200811835899</v>
       </c>
       <c r="D6" t="n">
-        <v>60.65924540229769</v>
+        <v>67.46177524502383</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>198.1647923545144</v>
+        <v>140.2544405241078</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.421390749300134</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>94.29686699290613</v>
+        <v>58.74778262212912</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.36890045708532</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.680171232593792</v>
+        <v>0.4113522880794135</v>
       </c>
       <c r="C2" t="n">
-        <v>7.17461222263569</v>
+        <v>2.839214360681776</v>
       </c>
       <c r="D2" t="n">
-        <v>14.53575650907827</v>
+        <v>7.786241042381453</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.16247139728623</v>
+        <v>3.725732537616646</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9770442543706</v>
+        <v>19.62022786937251</v>
       </c>
       <c r="D3" t="n">
-        <v>81.2445312649448</v>
+        <v>69.1788519797515</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.60500293219007</v>
+        <v>13.47743248390021</v>
       </c>
       <c r="C4" t="n">
-        <v>80.37961153750335</v>
+        <v>68.72724803579796</v>
       </c>
       <c r="D4" t="n">
-        <v>168.672109571236</v>
+        <v>151.3275728803076</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.72427743048944</v>
+        <v>17.59782759862408</v>
       </c>
       <c r="C5" t="n">
-        <v>181.6478689782661</v>
+        <v>173.3521008773806</v>
       </c>
       <c r="D5" t="n">
-        <v>153.7416904850505</v>
+        <v>135.5548142638784</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>9.257880851047425</v>
       </c>
       <c r="C6" t="n">
-        <v>281.8420944305828</v>
+        <v>262.3602929875092</v>
       </c>
       <c r="D6" t="n">
-        <v>81.26809320984674</v>
+        <v>73.49952362614172</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C7" t="n">
-        <v>264.638929409066</v>
+        <v>181.9954076655694</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>160.2212253330794</v>
+        <v>69.84644041863932</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.693514789825748</v>
+        <v>0.3848451000647496</v>
       </c>
       <c r="C2" t="n">
-        <v>4.689808783187013</v>
+        <v>10.76977231558751</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4507043117073</v>
+        <v>8.283005380730339</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.39670818797372</v>
+        <v>2.48382169174443</v>
       </c>
       <c r="C3" t="n">
-        <v>27.05205799052086</v>
+        <v>14.64276700884118</v>
       </c>
       <c r="D3" t="n">
-        <v>75.99218104722436</v>
+        <v>59.70989537229102</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.75891633757857</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="C4" t="n">
-        <v>75.9637103638012</v>
+        <v>57.76407142247383</v>
       </c>
       <c r="D4" t="n">
-        <v>170.4716531131204</v>
+        <v>151.9274207276024</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.44862730977434</v>
+        <v>19.07044915499429</v>
       </c>
       <c r="C5" t="n">
-        <v>173.7447999590793</v>
+        <v>150.060136594125</v>
       </c>
       <c r="D5" t="n">
-        <v>170.0141586829414</v>
+        <v>158.282273617192</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.0164373357275</v>
+        <v>16.22141731727005</v>
       </c>
       <c r="C6" t="n">
-        <v>301.3238958736566</v>
+        <v>270.2898691947107</v>
       </c>
       <c r="D6" t="n">
-        <v>94.99390786292139</v>
+        <v>96.76498072138264</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.11516758103314</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>314.9436817746725</v>
+        <v>283.7427579860046</v>
       </c>
       <c r="D7" t="n">
-        <v>47.31042186765379</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.588287859022091</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>209.1220784816131</v>
+        <v>153.2949952796182</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>67.00624431025328</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.386628669023996</v>
+        <v>0.430005494460103</v>
       </c>
       <c r="C2" t="n">
-        <v>19.01056254503524</v>
+        <v>10.12181883078462</v>
       </c>
       <c r="D2" t="n">
-        <v>11.29893432817654</v>
+        <v>8.661959994569608</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.192684591939633</v>
+        <v>1.884955592153876</v>
       </c>
       <c r="C3" t="n">
-        <v>22.86490403190821</v>
+        <v>28.85356502781376</v>
       </c>
       <c r="D3" t="n">
-        <v>69.0070461315083</v>
+        <v>53.20581683165589</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.13430381349934</v>
+        <v>7.504479451262619</v>
       </c>
       <c r="C4" t="n">
-        <v>72.05831799630738</v>
+        <v>46.91575929054657</v>
       </c>
       <c r="D4" t="n">
-        <v>167.2937357944735</v>
+        <v>146.3884001802419</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.29507375728434</v>
+        <v>17.67145867644259</v>
       </c>
       <c r="C5" t="n">
-        <v>159.2394776288327</v>
+        <v>128.584405563726</v>
       </c>
       <c r="D5" t="n">
-        <v>186.0411899547706</v>
+        <v>175.3155962858742</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.85921883432777</v>
+        <v>20.68935111929729</v>
       </c>
       <c r="C6" t="n">
-        <v>292.7100415165951</v>
+        <v>254.0684518774406</v>
       </c>
       <c r="D6" t="n">
-        <v>116.6895503790716</v>
+        <v>120.4732060312389</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>363.1524027917121</v>
+        <v>336.9819542396049</v>
       </c>
       <c r="D7" t="n">
-        <v>57.85046522044755</v>
+        <v>59.16797063954677</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>289.8168310321796</v>
+        <v>257.6056888558418</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>133.7906136393468</v>
+        <v>116.5953025994639</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.094869674413446</v>
+        <v>3.899501881268331</v>
       </c>
       <c r="C2" t="n">
-        <v>5.378995671568275</v>
+        <v>11.22726674576652</v>
       </c>
       <c r="D2" t="n">
-        <v>22.71371488545421</v>
+        <v>7.641924129857172</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.723948968657399</v>
+        <v>0.5262167694762904</v>
       </c>
       <c r="C2" t="n">
-        <v>11.10160303962293</v>
+        <v>24.65463009675015</v>
       </c>
       <c r="D2" t="n">
-        <v>8.405723843761191</v>
+        <v>12.62822071972672</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.01520924164921</v>
+        <v>1.644427404613407</v>
       </c>
       <c r="C3" t="n">
-        <v>40.50200153870216</v>
+        <v>33.58068022376215</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7341613274567</v>
+        <v>48.44434046605886</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.92781800043802</v>
+        <v>5.602834148136547</v>
       </c>
       <c r="C4" t="n">
-        <v>101.3359980323558</v>
+        <v>58.33839382945821</v>
       </c>
       <c r="D4" t="n">
-        <v>172.5775019387298</v>
+        <v>140.6962269910189</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.75891633757857</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C5" t="n">
-        <v>242.5653140267807</v>
+        <v>108.4585776266664</v>
       </c>
       <c r="D5" t="n">
-        <v>169.4987411382118</v>
+        <v>183.5868206941536</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.13462260866883</v>
+        <v>21.9774041072691</v>
       </c>
       <c r="C6" t="n">
-        <v>293.6760812575739</v>
+        <v>233.942623940381</v>
       </c>
       <c r="D6" t="n">
-        <v>89.1574177611741</v>
+        <v>142.9336300089974</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.311835917051991</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C7" t="n">
-        <v>203.7941336906656</v>
+        <v>349.9773486007199</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>75.03792227869646</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>98.55274329081605</v>
+        <v>340.5535523876548</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>199.4656080626414</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>81.42615459023047</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.69708192774424</v>
+        <v>4.438481370899829</v>
       </c>
       <c r="C2" t="n">
-        <v>8.505862109594364</v>
+        <v>14.09200654675872</v>
       </c>
       <c r="D2" t="n">
-        <v>33.91251094779757</v>
+        <v>31.09784027972196</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.70810213666921</v>
+        <v>6.445173678380311</v>
       </c>
       <c r="C3" t="n">
-        <v>13.55302705712722</v>
+        <v>22.16786316189298</v>
       </c>
       <c r="D3" t="n">
-        <v>22.21695054710532</v>
+        <v>8.261406931236911</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39647919431755</v>
+        <v>11.67811001116911</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13450872319189</v>
+        <v>59.9476313906681</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576056375802065</v>
+        <v>0.778540667411274</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.53371089821177</v>
+        <v>2.590832191507333</v>
       </c>
       <c r="C2" t="n">
-        <v>11.04367992507237</v>
+        <v>9.318749208710724</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57434776918016</v>
+        <v>27.41039590257094</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.25635932399543</v>
+        <v>12.10985793188441</v>
       </c>
       <c r="C3" t="n">
-        <v>25.82487336021235</v>
+        <v>43.73195148567417</v>
       </c>
       <c r="D3" t="n">
-        <v>45.33220024359647</v>
+        <v>33.55122779263475</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.27398972494287</v>
+        <v>8.078801858247003</v>
       </c>
       <c r="C4" t="n">
-        <v>21.21164089795658</v>
+        <v>36.02915899815369</v>
       </c>
       <c r="D4" t="n">
-        <v>26.71237328485147</v>
+        <v>18.5314696653628</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43504081685015</v>
+        <v>13.62574956472906</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11128034663768</v>
+        <v>73.73935058559256</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249482277231611</v>
+        <v>1.60302936055636</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.036365722786137</v>
+        <v>1.833904711533042</v>
       </c>
       <c r="C2" t="n">
-        <v>9.967684441217866</v>
+        <v>6.801548095021903</v>
       </c>
       <c r="D2" t="n">
-        <v>31.10176727053895</v>
+        <v>28.14376143764331</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64414966717292</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="C3" t="n">
-        <v>36.03014074585794</v>
+        <v>39.10791979867169</v>
       </c>
       <c r="D3" t="n">
-        <v>56.87264450701772</v>
+        <v>48.46888415866503</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.85428473361074</v>
+        <v>17.1913840490659</v>
       </c>
       <c r="C4" t="n">
-        <v>46.34143688356219</v>
+        <v>80.7624931421596</v>
       </c>
       <c r="D4" t="n">
-        <v>43.39324852770901</v>
+        <v>31.81746134693488</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.449321653375552</v>
+        <v>7.657632093125122</v>
       </c>
       <c r="C5" t="n">
-        <v>24.29825568010856</v>
+        <v>41.33157834879072</v>
       </c>
       <c r="D5" t="n">
-        <v>32.22586839190156</v>
+        <v>26.8262560185441</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72210103500493</v>
+        <v>14.82927166861807</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0048163135301</v>
+        <v>87.32793315963976</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180525258751232</v>
+        <v>2.471545278103012</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.80761850769663</v>
+        <v>2.790126975469435</v>
       </c>
       <c r="C2" t="n">
-        <v>12.00382917982575</v>
+        <v>6.200718500022854</v>
       </c>
       <c r="D2" t="n">
-        <v>28.41374205631119</v>
+        <v>23.86432319483147</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46390900021901</v>
+        <v>8.099418560036186</v>
       </c>
       <c r="C3" t="n">
-        <v>37.49294482518569</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D3" t="n">
-        <v>67.85840131753953</v>
+        <v>59.73443906489717</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.88279647476291</v>
+        <v>18.74843590800134</v>
       </c>
       <c r="C4" t="n">
-        <v>70.36087621566466</v>
+        <v>90.71741486322226</v>
       </c>
       <c r="D4" t="n">
-        <v>61.12066682329367</v>
+        <v>48.93226907506953</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.00310947402876</v>
+        <v>17.10695374650068</v>
       </c>
       <c r="C5" t="n">
-        <v>56.52412407201012</v>
+        <v>101.7336058525757</v>
       </c>
       <c r="D5" t="n">
-        <v>39.785325714602</v>
+        <v>32.2749557771139</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.298132506921544</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="C6" t="n">
-        <v>25.92206638293279</v>
+        <v>40.09064925062275</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>32.92585450502953</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.04286240828414</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>48.40016181936776</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03670225542043</v>
+        <v>16.05941219891515</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6680099520285</v>
+        <v>100.5826342984686</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012234085140141</v>
+        <v>3.380928883982137</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.914048170382785</v>
+        <v>3.61970378555799</v>
       </c>
       <c r="C2" t="n">
-        <v>8.338964999872408</v>
+        <v>4.742823159216341</v>
       </c>
       <c r="D2" t="n">
-        <v>24.08030768976576</v>
+        <v>37.43600345833937</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.57895340806514</v>
+        <v>8.816094384136358</v>
       </c>
       <c r="C3" t="n">
-        <v>39.98658399397259</v>
+        <v>27.32203860918873</v>
       </c>
       <c r="D3" t="n">
-        <v>70.56802498126073</v>
+        <v>64.20139111922016</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.00743737547325</v>
+        <v>17.01270596689298</v>
       </c>
       <c r="C4" t="n">
-        <v>69.56958756604172</v>
+        <v>83.44266437475339</v>
       </c>
       <c r="D4" t="n">
-        <v>68.47199363269378</v>
+        <v>65.3451271946677</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.9905266803228</v>
+        <v>22.67837196810132</v>
       </c>
       <c r="C5" t="n">
-        <v>70.61220362795184</v>
+        <v>136.6101930459437</v>
       </c>
       <c r="D5" t="n">
-        <v>42.11697651218817</v>
+        <v>41.96971435655115</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.740900721536855</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>39.00385454202154</v>
+        <v>101.7159343938993</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>35.38120551335081</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>18.92416874706152</v>
+        <v>37.84833749412304</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>24.78422079371073</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>32.88363935374691</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.043900814260399</v>
+        <v>17.3101031528488</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03657013369124</v>
+        <v>113.3811756511597</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40243800891275</v>
+        <v>4.327525788212201</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.28434698133308</v>
+        <v>3.73064127613788</v>
       </c>
       <c r="C2" t="n">
-        <v>5.076617378660257</v>
+        <v>10.6333093846972</v>
       </c>
       <c r="D2" t="n">
-        <v>21.01038261858599</v>
+        <v>38.34804707558466</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14760631300229</v>
+        <v>10.43597809614359</v>
       </c>
       <c r="C3" t="n">
-        <v>35.31346492175777</v>
+        <v>22.59983215176158</v>
       </c>
       <c r="D3" t="n">
-        <v>73.74397880449916</v>
+        <v>76.61068210089985</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.41057582902019</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C4" t="n">
-        <v>87.59054842519618</v>
+        <v>74.94269275138453</v>
       </c>
       <c r="D4" t="n">
-        <v>89.5687700492535</v>
+        <v>79.30754304446585</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.84450831429729</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C5" t="n">
-        <v>105.513334513926</v>
+        <v>144.9795922246477</v>
       </c>
       <c r="D5" t="n">
-        <v>57.60404654668161</v>
+        <v>54.33973543006097</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.91198686398306</v>
+        <v>21.9774041072691</v>
       </c>
       <c r="C6" t="n">
-        <v>81.26809320984674</v>
+        <v>154.8883718036108</v>
       </c>
       <c r="D6" t="n">
-        <v>39.04410619789565</v>
+        <v>40.01014593887452</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>40.36357511240336</v>
+        <v>88.99150239915636</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>22.5311098124643</v>
+        <v>36.80081269369168</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.25837863141702</v>
+        <v>17.68830577246674</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3056783009516</v>
+        <v>125.5869709845139</v>
       </c>
       <c r="D21" t="n">
-        <v>5.443783973562765</v>
+        <v>5.306491731740023</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.651119712093887</v>
+        <v>3.357577148524092</v>
       </c>
       <c r="C2" t="n">
-        <v>7.948229413582177</v>
+        <v>6.804493338134643</v>
       </c>
       <c r="D2" t="n">
-        <v>18.82010349041136</v>
+        <v>30.50584641406114</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24792450528471</v>
+        <v>12.50746575210436</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1488501026138</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="D3" t="n">
-        <v>73.30710107610933</v>
+        <v>83.18839171935349</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>11.62683806139498</v>
       </c>
       <c r="C4" t="n">
-        <v>88.07553179109411</v>
+        <v>116.9703302224862</v>
       </c>
       <c r="D4" t="n">
-        <v>104.6160171122444</v>
+        <v>72.27528423894593</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.5203927031756</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="C5" t="n">
-        <v>136.5365619681252</v>
+        <v>92.55426481786806</v>
       </c>
       <c r="D5" t="n">
-        <v>76.74812677949441</v>
+        <v>39.5398887885403</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.64659618866693</v>
+        <v>7.728317927830893</v>
       </c>
       <c r="C6" t="n">
-        <v>126.269444477112</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="D6" t="n">
-        <v>48.06047711369836</v>
+        <v>25.35854320069512</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>81.38590293435632</v>
+        <v>25.87101550231194</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>38.97047512007713</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07031028627404</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.34153469455343</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.458637743942387</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.90967461935186</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.526308025949588</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
